--- a/data/modify.xlsx
+++ b/data/modify.xlsx
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -3431,7 +3431,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -18350,7 +18350,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -19061,7 +19061,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -19770,7 +19770,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -21666,7 +21666,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -22140,7 +22140,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -23325,7 +23325,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -24510,7 +24510,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -24747,7 +24747,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -25458,7 +25458,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -26880,7 +26880,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -28067,7 +28067,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -28545,7 +28545,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -29023,7 +29023,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -29262,7 +29262,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -29501,7 +29501,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -29979,7 +29979,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -30455,7 +30455,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -30929,7 +30929,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -31640,7 +31640,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -31877,7 +31877,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -32114,7 +32114,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -32351,7 +32351,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -32588,7 +32588,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -32825,7 +32825,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -33536,7 +33536,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -34010,7 +34010,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -34249,7 +34249,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -34488,7 +34488,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -34727,7 +34727,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -34966,7 +34966,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -35683,7 +35683,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -35922,7 +35922,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -36161,7 +36161,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -36402,7 +36402,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -36641,7 +36641,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -36880,7 +36880,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -37115,7 +37115,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -37350,7 +37350,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -38055,7 +38055,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -38290,7 +38290,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -38527,7 +38527,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -38762,7 +38762,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -38997,7 +38997,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -39236,7 +39236,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -39953,7 +39953,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -40192,7 +40192,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -40431,7 +40431,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -40672,7 +40672,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -40911,7 +40911,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -41150,7 +41150,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -41389,7 +41389,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I172" t="n">
@@ -41628,7 +41628,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -42106,7 +42106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -42345,7 +42345,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -42584,7 +42584,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -42825,7 +42825,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -43064,7 +43064,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I179" t="n">
@@ -43303,7 +43303,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -43542,7 +43542,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -43781,7 +43781,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -44259,7 +44259,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I184" t="n">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -44737,7 +44737,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -44978,7 +44978,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I187" t="n">
@@ -45217,7 +45217,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I188" t="n">
@@ -45456,7 +45456,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I189" t="n">
@@ -45695,7 +45695,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I190" t="n">
@@ -45934,7 +45934,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -46412,7 +46412,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I193" t="n">
@@ -46651,7 +46651,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -46890,7 +46890,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -47131,7 +47131,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I197" t="n">
@@ -47609,7 +47609,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I198" t="n">
@@ -47848,7 +47848,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I199" t="n">
@@ -48087,7 +48087,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I200" t="n">
@@ -48565,7 +48565,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I202" t="n">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I203" t="n">
@@ -49043,7 +49043,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -49284,7 +49284,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -49523,7 +49523,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I206" t="n">
@@ -49762,7 +49762,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I207" t="n">
